--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$22</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="138">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,9 +320,6 @@
   </si>
   <si>
     <t>family</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -573,21 +567,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -915,7 +894,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1018,7 +997,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>79</v>
       </c>
@@ -1121,7 +1100,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>86</v>
       </c>
@@ -1226,7 +1205,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -1247,7 +1226,7 @@
         <v>80</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>74</v>
@@ -1262,7 +1241,7 @@
         <v>28</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1331,12 +1310,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1434,12 +1413,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1468,7 +1447,7 @@
         <v>28</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1537,12 +1516,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1565,16 +1544,16 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1624,7 +1603,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1642,12 +1621,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1673,10 +1652,10 @@
         <v>81</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1727,7 +1706,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1739,21 +1718,21 @@
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
@@ -1766,7 +1745,7 @@
         <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>74</v>
@@ -1781,7 +1760,7 @@
         <v>28</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1850,12 +1829,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1953,12 +1932,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1987,7 +1966,7 @@
         <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2056,12 +2035,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2084,16 +2063,16 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2101,7 +2080,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2143,7 +2122,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2161,12 +2140,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2192,10 +2171,10 @@
         <v>81</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2246,7 +2225,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2258,21 +2237,21 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>74</v>
@@ -2285,7 +2264,7 @@
         <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>74</v>
@@ -2300,7 +2279,7 @@
         <v>28</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2369,12 +2348,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2472,12 +2451,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2506,7 +2485,7 @@
         <v>28</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2575,12 +2554,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2603,16 +2582,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2620,7 +2599,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>74</v>
@@ -2662,7 +2641,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2680,12 +2659,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2708,13 +2687,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2753,17 +2732,17 @@
         <v>74</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -2775,21 +2754,21 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>74</v>
@@ -2811,13 +2790,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2844,11 +2823,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2866,7 +2845,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -2878,18 +2857,18 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2912,16 +2891,16 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -2971,7 +2950,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -2989,12 +2968,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3017,13 +2996,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3074,7 +3053,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3086,31 +3065,13 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK22">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI21">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$16</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,166 +282,304 @@
     <t>Extension.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanName {http://interopsante.org/fhir/StructureDefinition/FrHumanName}
+</t>
+  </si>
+  <si>
+    <t>Name of a human - parts and usage</t>
+  </si>
+  <si>
+    <t>A human's name with the ability to identify parts and usage.</t>
+  </si>
+  <si>
+    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>EN (actually, PN)</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName</t>
+  </si>
+  <si>
+    <t>valueHumanName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanName
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.id</t>
+  </si>
+  <si>
+    <t>Extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.extension</t>
+  </si>
+  <si>
+    <t>Extension.value[x].extension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.use</t>
+  </si>
+  <si>
+    <t>Extension.value[x].use</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.text</t>
+  </si>
+  <si>
+    <t>Extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.family</t>
+  </si>
+  <si>
+    <t>Extension.value[x].family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.given</t>
+  </si>
+  <si>
+    <t>Extension.value[x].given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.prefix</t>
+  </si>
+  <si>
+    <t>Extension.value[x].prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.suffix</t>
+  </si>
+  <si>
+    <t>Extension.value[x].suffix</t>
+  </si>
+  <si>
+    <t>Parts that come after the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valueHumanName.period</t>
+  </si>
+  <si>
+    <t>Extension.value[x].period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Extension.extension:family</t>
-  </si>
-  <si>
-    <t>family</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:family.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:family.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:family.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:family.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:given</t>
-  </si>
-  <si>
-    <t>given</t>
-  </si>
-  <si>
-    <t>Extension.extension:given.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:given.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:given.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:given.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:suffix</t>
-  </si>
-  <si>
-    <t>suffix</t>
-  </si>
-  <si>
-    <t>Extension.extension:suffix.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:suffix.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:suffix.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:suffix.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Extension.extension:suffix.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
 </sst>
 </file>
@@ -567,6 +708,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -740,24 +896,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.1484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.1484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="45.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="27.703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.07421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="13.0859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="95.703125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -767,18 +923,18 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="90.21875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="25.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="40.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="19.48828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="30.98828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -894,7 +1050,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -997,7 +1153,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>79</v>
       </c>
@@ -1100,7 +1256,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>86</v>
       </c>
@@ -1109,14 +1265,14 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>74</v>
@@ -1128,17 +1284,15 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>91</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>74</v>
@@ -1175,19 +1329,19 @@
         <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AD4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AF4" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AC4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1199,28 +1353,26 @@
         <v>78</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>99</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>80</v>
@@ -1235,22 +1387,24 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>98</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="S5" t="s" s="2">
         <v>74</v>
@@ -1292,30 +1446,30 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1338,15 +1492,17 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N6" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N6" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>74</v>
@@ -1383,19 +1539,17 @@
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="AC6" s="2"/>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
@@ -1404,23 +1558,25 @@
         <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
@@ -1429,7 +1585,7 @@
         <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1441,13 +1597,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1486,42 +1642,42 @@
         <v>74</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1529,7 +1685,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>80</v>
@@ -1544,24 +1700,22 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>74</v>
@@ -1603,10 +1757,10 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>80</v>
@@ -1618,26 +1772,26 @@
         <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -1649,15 +1803,17 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>74</v>
@@ -1694,46 +1850,44 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
@@ -1748,22 +1902,26 @@
         <v>74</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>74</v>
       </c>
@@ -1787,13 +1945,13 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -1811,30 +1969,30 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1854,19 +2012,23 @@
         <v>74</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>74</v>
       </c>
@@ -1914,7 +2076,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -1923,52 +2085,54 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -2005,74 +2169,74 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2080,7 +2244,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2122,30 +2286,30 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2156,7 +2320,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -2165,18 +2329,20 @@
         <v>74</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
@@ -2225,34 +2391,32 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>125</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2261,27 +2425,29 @@
         <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>74</v>
@@ -2330,7 +2496,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2342,18 +2508,18 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2373,19 +2539,23 @@
         <v>74</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2433,7 +2603,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2442,636 +2612,34 @@
         <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AC19" s="2"/>
-      <c r="AD19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="Y20" s="2"/>
-      <c r="Z20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q22" s="2"/>
-      <c r="R22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>97</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AK16">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI15">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="184">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,6 +253,12 @@
 </t>
   </si>
   <si>
+    <t>civiliteNomPrenomExercice</t>
+  </si>
+  <si>
+    <t>La civilité, le nom et le prénom sous lequels exerce le professionnel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -470,10 +476,10 @@
 </t>
   </si>
   <si>
-    <t>Family name (often called 'Surname')</t>
-  </si>
-  <si>
-    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+    <t>nomExercice</t>
+  </si>
+  <si>
+    <t>Nom sous lequel exerce le professionnel.</t>
   </si>
   <si>
     <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
@@ -495,10 +501,10 @@
 middle name</t>
   </si>
   <si>
-    <t>Given names (not always 'first'). Includes middle names</t>
-  </si>
-  <si>
-    <t>Given name.</t>
+    <t>prenomExercice</t>
+  </si>
+  <si>
+    <t>Prénom sous lequel exerce le professionnel.</t>
   </si>
   <si>
     <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
@@ -537,10 +543,10 @@
     <t>Extension.value[x].suffix</t>
   </si>
   <si>
-    <t>Parts that come after the name</t>
-  </si>
-  <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+    <t>civiliteExercice</t>
+  </si>
+  <si>
+    <t>Civilité d’exercice du professionnel.</t>
   </si>
   <si>
     <t>HumanName.suffix</t>
@@ -1081,10 +1087,10 @@
         <v>77</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1144,7 +1150,7 @@
         <v>76</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
         <v>74</v>
@@ -1155,10 +1161,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1169,7 +1175,7 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1181,13 +1187,13 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1238,13 +1244,13 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>74</v>
@@ -1253,15 +1259,15 @@
         <v>74</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1284,13 +1290,13 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1329,19 +1335,19 @@
         <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1350,10 +1356,10 @@
         <v>76</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>74</v>
@@ -1361,10 +1367,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1372,10 +1378,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>74</v>
@@ -1387,16 +1393,16 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1446,13 +1452,13 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>74</v>
@@ -1461,15 +1467,15 @@
         <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1480,7 +1486,7 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1492,16 +1498,16 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1539,43 +1545,43 @@
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AC6" s="2"/>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI6" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>74</v>
@@ -1585,7 +1591,7 @@
         <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1597,13 +1603,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1654,30 +1660,30 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI7" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI7" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1688,7 +1694,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1700,13 +1706,13 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1757,13 +1763,13 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>74</v>
@@ -1772,19 +1778,19 @@
         <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1803,16 +1809,16 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1850,19 +1856,19 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1871,21 +1877,21 @@
         <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1896,31 +1902,31 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -1945,13 +1951,13 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -1969,30 +1975,30 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI10" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI10" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ10" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2003,7 +2009,7 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
@@ -2012,22 +2018,22 @@
         <v>74</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2076,62 +2082,62 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI11" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI11" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ11" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2181,34 +2187,34 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI12" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI12" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ12" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2218,25 +2224,25 @@
         <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2286,7 +2292,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2295,21 +2301,21 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2329,19 +2335,19 @@
         <v>74</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2391,7 +2397,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2400,21 +2406,21 @@
         <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2428,25 +2434,25 @@
         <v>76</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2496,7 +2502,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2505,21 +2511,21 @@
         <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2530,7 +2536,7 @@
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2539,22 +2545,22 @@
         <v>74</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>74</v>
@@ -2603,22 +2609,22 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI16" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
